--- a/source/reference_documents/working_material/example system/example system attack surface analysis issues.xlsx
+++ b/source/reference_documents/working_material/example system/example system attack surface analysis issues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charles.wilson/Documents/projects/AVCDL/source/reference_documents/working_material/example system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BA8C3C-7FA1-9343-83CF-1569F3CADE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9523DBA-C8E8-2C4A-9AD0-CD653767FAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38780" yWindow="16160" windowWidth="30240" windowHeight="18880" activeTab="3" xr2:uid="{DEA20EDE-F7A8-FC4F-9F8A-95A2B1030BD3}"/>
+    <workbookView xWindow="30300" yWindow="18980" windowWidth="30780" windowHeight="18140" activeTab="2" xr2:uid="{DEA20EDE-F7A8-FC4F-9F8A-95A2B1030BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="cover sheet" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>reason</t>
   </si>
@@ -207,6 +207,66 @@
   <si>
     <t>AVCDL/source/working_material/example system/images/source</t>
   </si>
+  <si>
+    <t>example system ASA element model</t>
+  </si>
+  <si>
+    <t>example system attack surface analysis model.xlsx</t>
+  </si>
+  <si>
+    <t>AVCDL/source/working_material/example system/</t>
+  </si>
+  <si>
+    <t>ESASAI-01</t>
+  </si>
+  <si>
+    <t>ESASAI-02</t>
+  </si>
+  <si>
+    <t>ESASAI-03</t>
+  </si>
+  <si>
+    <t>ESASAI-04</t>
+  </si>
+  <si>
+    <t>ESASAI-05</t>
+  </si>
+  <si>
+    <t>ESASAI-06</t>
+  </si>
+  <si>
+    <t>ESASAI-07</t>
+  </si>
+  <si>
+    <t>ESASAI-08</t>
+  </si>
+  <si>
+    <t>ESC-05</t>
+  </si>
+  <si>
+    <t>ESC-06</t>
+  </si>
+  <si>
+    <t>ESC-09</t>
+  </si>
+  <si>
+    <t>ESC-10</t>
+  </si>
+  <si>
+    <t>ESC-11</t>
+  </si>
+  <si>
+    <t>ESC-13</t>
+  </si>
+  <si>
+    <t>ESL-01</t>
+  </si>
+  <si>
+    <t>incorrect port number for protocol</t>
+  </si>
+  <si>
+    <t>incorrect protocol for authenticated communication</t>
+  </si>
 </sst>
 </file>
 
@@ -215,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -316,6 +376,24 @@
       <name val="Courier New"/>
       <family val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Courier New Bold"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -377,11 +455,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -410,49 +487,59 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,215 +875,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46733E74-9B11-424D-A209-B9C08CC2B355}">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="31.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="63" x14ac:dyDescent="0.75">
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="2:11" ht="63">
+      <c r="B2" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-    </row>
-    <row r="4" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B4" s="24" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+    </row>
+    <row r="4" spans="2:11" ht="32">
+      <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-    </row>
-    <row r="6" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B6" s="24" t="s">
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="2:11" ht="32">
+      <c r="B6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-    </row>
-    <row r="8" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B8" s="24" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+    </row>
+    <row r="8" spans="2:11" ht="32">
+      <c r="B8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="30" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-    </row>
-    <row r="10" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="2:11" ht="32">
+      <c r="B10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="33" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-    </row>
-    <row r="12" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B12" s="24" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+    </row>
+    <row r="12" spans="2:11" ht="32">
+      <c r="B12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-    </row>
-    <row r="14" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B14" s="24" t="s">
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+    </row>
+    <row r="14" spans="2:11" ht="32">
+      <c r="B14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="31">
+      <c r="C14" s="20"/>
+      <c r="D14" s="30">
         <v>45806</v>
       </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-    </row>
-    <row r="16" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B16" s="24" t="s">
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+    </row>
+    <row r="16" spans="2:11" ht="32">
+      <c r="B16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="32">
+      <c r="C16" s="20"/>
+      <c r="D16" s="23">
         <v>1</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-    </row>
-    <row r="17" spans="2:11" ht="134" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="2:11" ht="32" x14ac:dyDescent="0.4">
-      <c r="B18" s="21" t="s">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+    </row>
+    <row r="17" spans="2:11" ht="134" customHeight="1">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:11" ht="32">
+      <c r="B18" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1021,119 +1108,119 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6ACBA90-8F21-6547-8383-D56B951176BB}">
   <dimension ref="A2:G20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="45.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="63" x14ac:dyDescent="0.75">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="1:7" ht="63">
+      <c r="B2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1"/>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="11">
+    <row r="5" spans="1:7">
+      <c r="B5" s="10">
         <v>1</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="11"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="17"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="11"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="17"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="11"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="11"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="11"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="11"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="11"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="11"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="17"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="11"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="17"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="11"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="11"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="17"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="11"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="11"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="17"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="11"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="17"/>
+    <row r="6" spans="1:7">
+      <c r="B6" s="10"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="10"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="10"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="10"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="10"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="10"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="10"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="10"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="10"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="10"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="10"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="10"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="10"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="10"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="10"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1145,114 +1232,127 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9E43A7-A2A5-FA40-988F-770692138751}">
-  <dimension ref="A2:G20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:J20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="46.33203125" customWidth="1"/>
-    <col min="4" max="4" width="54.83203125" customWidth="1"/>
+    <col min="2" max="2" width="59.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="63" x14ac:dyDescent="0.75">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="1:10" ht="63">
+      <c r="B2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1"/>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="13"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="13"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="13"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="13"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="13"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="13"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="13"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="13"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="13"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="13"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="13"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="13"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="13"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="13"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="13"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="13"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="5"/>
+    <row r="5" spans="1:10" ht="17">
+      <c r="B5" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="12"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="12"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="12"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="12"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="12"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="12"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="12"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="12"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="12"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="12"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="12"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="12"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="12"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1265,29 +1365,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF26DBA4-9ED6-7C40-A69D-485B34325BAD}">
   <dimension ref="B2:K20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="37.6640625" customWidth="1"/>
     <col min="6" max="6" width="46.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="63" x14ac:dyDescent="0.75">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="2:11" ht="63">
+      <c r="B2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="4" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="4" spans="2:11" s="1" customFormat="1">
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1304,117 +1405,185 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="34"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="34"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="34"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="34"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="34"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="34"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="34"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="34"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="34"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="34"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B17" s="34"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" s="34"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" s="34"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" s="34"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+    <row r="5" spans="2:11">
+      <c r="B5" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="24"/>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="24"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1423,7 +1592,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{CFA2D08E-C404-E248-A0EE-994173502854}">
           <x14:formula1>
             <xm:f>legend!$A$2:$A$11</xm:f>
@@ -1445,7 +1614,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E47EDA-BFD6-E448-BD76-322D521CE805}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
@@ -1453,7 +1622,7 @@
     <col min="4" max="4" width="44.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -1467,172 +1636,172 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
+      <c r="D4" s="18"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-    </row>
-    <row r="25" spans="1:4" ht="380" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="23" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+    </row>
+    <row r="25" spans="1:4" ht="380" customHeight="1">
+      <c r="B25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>2</v>
       </c>
     </row>
